--- a/Result/checksun_type/電池芯.xlsx
+++ b/Result/checksun_type/電池芯.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>39.46</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>41.04</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>45.88</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>41.04</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>45.88</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>23119.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>40070.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>40070.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>70067.5</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>51403.08</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>51403.08</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-1501.124055388631</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>23119</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>23119.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>40.38</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>41.31</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>46.26</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>41.31</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>46.26</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>12475.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>105990.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>105990.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>69931.1</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>51915.04</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>51915.04</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>1668.912755245285</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>12475</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>12475.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>41.02</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>41.57</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>46.66</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>41.57</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>46.66</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>17252.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>116778.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>116778</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>75994.1</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>53027.3</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>53027.3</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>7278.361314892114</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>17252</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>17252.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>40.82</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>41.89</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>47.07</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>41.89</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>47.07</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>41699.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>118539.4</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>118539.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>76074.7</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>53934.22</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>53934.22</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>14520.09635314145</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>41699</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>41699.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>40.51000000000001</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>42.29</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>47.47</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>42.29</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>47.47</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>105808.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>117623.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>117623</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>73632.6</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>53938.18</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>53938.18</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>21727.53582374257</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>105808</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>105808.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>40.31</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>42.66</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>47.81</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>42.66</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>47.81</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>352717.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>100064.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>100064.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>65241.2</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>52894.76</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>52894.76</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>24379.07307375336</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>352717</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>352717.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>39.54</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>42.81</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>48.12</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>42.81</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>48.12</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>66414.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>33872.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>33872</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>32562.6</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>50742.64</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>50742.64</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>841.766535420451</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>66414</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>66414.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>38.86999999999999</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>42.99</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>48.51</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>42.99</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>48.51</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>26059.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>35210.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>35210.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>29556.1</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>59923.7</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>59923.7</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-2137.698752748696</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>26059</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>26059.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>39.42999999999999</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>43.38</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>48.89</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>43.38</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>48.89</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>37117.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>33610.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>33610</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>29799.9</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>63678.86</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>63678.86</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-1993.981351820741</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>37117</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>37117.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>40.3</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>43.9</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>49.18</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>49.18</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>18015.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>29642.2</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>29642.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>28117.6</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>65230.04</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>65230.04</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-2902.242873644354</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>18015</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>18015.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>40.96</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>44.26</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>49.48</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>44.26</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>49.48</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>21755.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>30418.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>30418</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>28980.5</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>69462.72</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>69462.72</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-2049.464945047934</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>21755</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>21755.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>35.76000000000001</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>38.1</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>42.71</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>42.71</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>20505311.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>23688960.4</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>23688960.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>27902811.3</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>67461101.26</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>67461101.26000001</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-6085963.661411732</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>20505311</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>20505311.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>35.6</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>38.31</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>43.06</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>38.31</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>43.06</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>19520578.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>25882649.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>25882649.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>28026820.3</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>87390993.54</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>87390993.54000001</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-6268515.36665557</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>19520578</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>19520578.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>35.68</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>43.44</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>43.44</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>15906906.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>32681259.2</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>32681259.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>28616956.7</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>102357221.12</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>102357221.12</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-6199920.861051921</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>15906906</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>15906906.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>36.14</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>39.01</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>43.82</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>39.01</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>43.82</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>31258786.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>34867870.0</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>34867870</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>30454113.9</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>108821129.02</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>108821129.02</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-5493323.822294854</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>31258786</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>31258786.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>36.7</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>39.42</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>44.19</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>39.42</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>44.19</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>31253221.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>32910582.4</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>32910582.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>30210832.4</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>112937471.28</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>112937471.28</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-5932553.630417094</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>31253221</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>31253221.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>37.04000000000001</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>39.79</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>44.53</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>39.79</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>44.53</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>31473755.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>32116662.2</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>32116662.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>31678631.9</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>123037166.28</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>123037166.28</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-6347551.619505391</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>31473755</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>31473755.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>37.73</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>40.09</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>44.85</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>40.09</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>44.85</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>53513628.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>30170991.4</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>30170991.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>35280490.3</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>126147244.34</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>126147244.34</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-6737336.260363467</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>53513628</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>53513628.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>38.27</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>40.35</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>45.19</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>40.35</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>45.19</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>26839960.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>24552654.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>24552654.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>42020759.3</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>129332318.02</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>129332318.02</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-9414967.273719177</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>26839960</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>26839960.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>38.76000000000001</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>40.54</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>45.52</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>40.54</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>45.52</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>21472348.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>26040357.8</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>26040357.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>41723861.2</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>133805365.86</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>133805365.86</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-10046012.60445165</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>21472348</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>21472348.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>39.08</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>40.76</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>45.81</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>40.76</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>45.81</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>27283620.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>27511082.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>27511082.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>42387390.4</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>137208707.58</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>137208707.58</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-10013618.48391049</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>27283620</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>27283620.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>39.44</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>40.92</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>46.13</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>40.92</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>46.13</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>21745401.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>31240601.6</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>31240601.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>43228307.2</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>141227523.72</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>141227523.72</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-10232348.22299773</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>21745401</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>21745401.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>34.27</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>32.35</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>32.64</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>32.64</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>30752.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>26021.8</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>26021.8</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>27135.3</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>14215.12</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>14215.12</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>1676.657039741152</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>30752</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>30752.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>33.98</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>32.19</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>32.61</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>32.19</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>32.61</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>15599.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>23408.4</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>23408.4</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>25268.3</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>14319.64</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>14319.64</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>1114.689186374952</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>15599</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>15599.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>33.77</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>32.07</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>32.62</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>32.07</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>32.62</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>9517.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>24723.6</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>24723.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>24634.6</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>14301.02</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>14301.02</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>1895.603353481278</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>9517</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>9517.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>33.68</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>31.99</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>32.64</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>31.99</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>32.64</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>31971.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>27396.0</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>27396</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>24460.1</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>14465.96</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>14465.96</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>3595.137758151694</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>31971</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>31971.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>33.58</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>31.91</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>32.67</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>31.91</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>32.67</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>42270.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>26727.6</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>26727.6</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>22014.3</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>14159.48</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>14159.48</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>3488.860559175446</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>42270</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>42270.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>33.34</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>31.81</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>32.67</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>32.67</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>17685.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>28248.8</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>28248.8</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>18790.2</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>13569.2</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>13569.2</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>2108.9695406674</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>17685</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>17685.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>32.92999999999999</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>31.75</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>32.7</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>32.7</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>22175.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>27128.2</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>27128.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>17701.2</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>13365.52</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>13365.52</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>2696.4834592035</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>22175</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>22175.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>32.44</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>31.71</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>32.72</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>31.71</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>32.72</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>22879.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>24545.6</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>24545.6</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>16522.3</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>13109.9</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>13109.9</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>2958.414647854945</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>22879</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>22879.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>31.82</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>31.66</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>32.74</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>32.74</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>28629.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>21524.2</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>21524.2</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>15788.2</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>12943.64</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>12943.64</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>3151.51582279076</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>28629</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>28629.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>31.32999999999999</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>31.61</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>32.78</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>32.78</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>49876.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>17301.0</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>17301</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>13897.0</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>12734.7</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>12734.7</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>2698.74907902797</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>49876</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>49876.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>30.82</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>31.55</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>32.8</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>32.8</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>12082.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>9331.6</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>9331.6</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>10294.0</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>11920.4</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>11920.4</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-320.9087363127292</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>12082</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>12082.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>99.47999999999999</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>102.82</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>105.0</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>102.82</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>105</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>103180579.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>116147614.4</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>116147614.4</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>176548720.3</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>201428975.56</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>201428975.56</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-25860202.92993152</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>103180579</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>103180579.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>98.94</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>103.24</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>105.06</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>103.24</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>105.06</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>78066930.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>134482037.6</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>134482037.6</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>193869170.8</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>205225010.12</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>205225010.12</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-24317788.82020301</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>78066930</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>78066930.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>98.72</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>103.7</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>105.23</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>105.23</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>136094275.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>162561404.6</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>162561404.6</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>195664628.6</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>209197245.52</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>209197245.52</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-18555099.52701217</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>136094275</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>136094275.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>98.9</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>104.3</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>105.44</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>105.44</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>116900919.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>222301963.2</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>222301963.2</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>191158060.8</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>220229469.28</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>220229469.28</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-15877219.6607748</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>116900919</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>116900919.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>99.6</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>104.8</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>105.6</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>146495369.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>240594220.2</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>240594220.2</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>198554746.8</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>221461486.3</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>221461486.3</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-9428202.435408056</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>146495369</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>146495369.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>100.4</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>105.28</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>105.69</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>105.28</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>105.69</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>194852695.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>236949826.2</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>236949826.2</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>211794368.0</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>221171326.8</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>221171326.8</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-3049433.097905278</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>194852695</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>194852695.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>101.84</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>105.81</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>105.84</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>105.81</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>105.84</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>218463765.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>253256304.0</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>253256304</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>212975569.9</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>219688213.02</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>219688213.02</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>990860.7805953324</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>218463765</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>218463765.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>102.86</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>106.24</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>106.24</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>106</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>434797068.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>228767852.6</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>228767852.6</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>230869656.9</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>217695178.8</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>217695178.8</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>4197563.793432087</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>434797068</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>434797068.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>103.8</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>106.6</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>106.11</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>106.11</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>208362204.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>160014158.4</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>160014158.4</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>237292886.2</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>210329621.68</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>210329621.68</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-14549913.0737094</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>208362204</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>208362204.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>104.0</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>106.8</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>106.18</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>106.18</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>128273399.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>156515273.4</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>156515273.4</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>280273763.1</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>208482988.26</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>208482988.26</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-16551504.84556478</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>128273399</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>128273399.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>104.0</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>106.85</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>106.24</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>106.24</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>276385084.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>186638909.8</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>186638909.8</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>285043227.5</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>208948816.74</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>208948816.74</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-10238853.09658802</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>276385084</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>276385084.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【c】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>804.2</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>783.55</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>695.92</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>783.55</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>695.92</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>3873207064.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>9792069338.8</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>9792069338.799999</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>6844419299.3</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>3738324553.72</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>3738324553.72</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>1072087242.743657</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>3873207064</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>3873207064.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>798.2</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>782.95</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>691.4</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>782.95</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>691.4</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>6366567274.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>9789142521.8</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>9789142521.799999</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>6940776945.3</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>3685793658.42</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>3685793658.42</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>1641726702.107907</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>6366567274</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>6366567274.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>781.6</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>778.6</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>686.42</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>778.6</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>686.42</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>32037210452.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>9363145708.2</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>9363145708.200001</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>6664202888.6</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>3594108024.84</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>3594108024.84</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>2129718525.052984</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>32037210452</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>32037210452.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>774.4</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>775.0</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>681.74</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>775</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>681.74</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>3219178175.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>3630962812.8</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>3630962812.8</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>3679090269.2</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>2987313106.58</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>2987313106.58</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>362270.0083417892</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>3219178175</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>3219178175.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>776.6</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>770.9</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>677.66</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>770.9</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>677.66</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>3464183729.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>3719056022.0</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>3719056022</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>3577925548.1</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>2944835131.88</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>2944835131.88</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>46058139.97998571</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>3464183729</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>3464183729.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>776.4</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>765.15</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>672.94</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>765.15</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>672.9400000000001</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>3858572979.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>3896769259.8</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>3896769259.8</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>3649778255.7</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>2912273920.24</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>2912273920.24</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>83442425.58304882</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>3858572979</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>3858572979.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>782.0</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>760.5</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>668.4</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>760.5</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>668.4</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>4236583206.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>4092411368.8</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>4092411368.8</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>3704598909.3</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>2852984228.02</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>2852984228.02</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>91612470.1737442</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>4236583206</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>4236583206.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>784.8</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>756.0</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>664.4</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>756</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>664.4</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>3376295975.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>3965260069.0</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>3965260069</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>3671040265.3</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>2794575964.04</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>2794575964.04</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>59510992.76138973</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>3376295975</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>3376295975.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>778.8</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>750.4</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>660.04</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>750.4</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>660.04</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>3659644221.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>3727217725.6</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>3727217725.6</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>3740494004.2</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>2769663405.96</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>2769663405.96</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>103699978.6094055</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>3659644221</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>3659644221.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>770.0</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>745.85</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>655.52</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>745.85</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>655.52</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>4352749918.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>3436795074.2</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>3436795074.2</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>3814140943.9</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>2735034261.96</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>2735034261.96</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>132764789.9419494</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>4352749918</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>4352749918.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>759.2</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>739.85</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>651.0</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>739.85</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>651</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>4836783524.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>3402787251.6</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>3402787251.6</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>3884644605.1</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>2738363958.58</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>2738363958.58</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>95283024.66908503</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>4836783524</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>4836783524.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>919.4</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>948.95</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>947.82</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>948.95</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>947.8200000000001</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>10702402903.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>13777681330.2</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>13777681330.2</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>13184190874.5</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>14165986897.28</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>14165986897.28</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-288049536.2624874</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>10702402903</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>10702402903.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>909.2</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>954.7</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>945.54</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>954.7</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>945.54</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>9579043601.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>13831910429.6</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>13831910429.6</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>13509805904.0</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>14413977761.06</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>14413977761.06</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-94238805.57345963</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>9579043601</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>9579043601.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>906.8</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>962.95</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>944.08</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>962.95</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>944.08</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>16911194399.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>14386844246.4</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>14386844246.4</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>13675683609.2</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>14618581897.64</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>14618581897.64</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>306359263.681345</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>16911194399</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>16911194399.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>911.4</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>971.8</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>941.9</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>971.8</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>941.9</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>15812987742.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>13146559354.4</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>13146559354.4</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>13118876980.5</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>14614553602.28</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>14614553602.28</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>82113231.98530579</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>15812987742</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>15812987742.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>916.8</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>977.55</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>938.52</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>977.55</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>938.52</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>15882778006.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>13620510362.4</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>13620510362.4</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>12470961715.4</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>14466055493.78</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>14466055493.78</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-123505858.3299389</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>15882778006</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>15882778006.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>917.6</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>980.85</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>933.96</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>980.85</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>933.96</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>10973548400.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>12590700418.8</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>12590700418.8</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>11918833012.0</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>14368721493.28</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>14368721493.28</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-420314020.6970749</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>10973548400</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>10973548400.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>932.2</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>987.15</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>929.9</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>987.15</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>929.9</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>12353712685.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>13187701378.4</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>13187701378.4</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>12539817288.3</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>14292572173.18</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>14292572173.18</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-303325579.8395176</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>12353712685</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>12353712685.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>947.0</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>993.0</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>925.54</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>993</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>925.54</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>10709769939.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>12964522972.0</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>12964522972</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>13184192924.4</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>14209168625.62</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>14209168625.62</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-273240924.15588</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>10709769939</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>10709769939.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>960.2</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>997.15</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>920.92</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>997.15</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>920.92</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>18182742782.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>13091194606.6</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>13091194606.6</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>13748861147.6</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>14155319682.02</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>14155319682.02</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-44367517.38797188</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>18182742782</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>18182742782.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>968.8</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>1002.3</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>916.24</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>1002.3</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>916.24</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>10733728288.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>11321413068.4</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>11321413068.4</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>14033372540.0</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>13994353884.38</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>13994353884.38</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-516496615.2771072</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>10733728288</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>10733728288.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>972.8</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>1005.15</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>911.3</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>1005.15</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>911.3</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>13958553198.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>11246965605.2</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>11246965605.2</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>15377407355.7</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>13940555876.02</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>13940555876.02</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-374411751.6445465</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>13958553198</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>13958553198.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
